--- a/Doumentation/Scan4Discount_Test_Scenarios.xlsx
+++ b/Doumentation/Scan4Discount_Test_Scenarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software Testing\Interview Prep\Projects\Scan4Discount\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software Testing\Interview Prep\Projects\Scan4Discount\Doumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC937324-4422-45BD-B621-FEACE09319E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D29F044-F33D-4E88-B4F1-6960CC4A8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BC929835-6C54-46C2-8466-B2E1D1A39176}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="190">
   <si>
     <t xml:space="preserve">Project Name:   </t>
   </si>
@@ -606,6 +606,9 @@
   </si>
   <si>
     <t>Browser Launch</t>
+  </si>
+  <si>
+    <t>Application launch</t>
   </si>
 </sst>
 </file>
@@ -649,7 +652,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -760,19 +763,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBB691"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2FCCB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1DEE3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE9A9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -945,6 +990,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -955,16 +1042,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDEE9A9"/>
+      <color rgb="FFA1DEE3"/>
+      <color rgb="FF79FFFF"/>
+      <color rgb="FFC1FFFF"/>
+      <color rgb="FF61FFFF"/>
+      <color rgb="FFE0C0A0"/>
+      <color rgb="FFFFFFCC"/>
       <color rgb="FFAAA490"/>
       <color rgb="FF97B0FF"/>
       <color rgb="FFFFC1E0"/>
-      <color rgb="FFFF99CC"/>
-      <color rgb="FFE0C0A0"/>
-      <color rgb="FFDAB48E"/>
-      <color rgb="FFB4FADF"/>
-      <color rgb="FF7AF6C7"/>
-      <color rgb="FFFFFF66"/>
-      <color rgb="FFFFCCCC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2165,44 +2252,44 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="60" t="s">
         <v>173</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="60" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="56" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="58" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2694,212 +2781,212 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="44" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="42" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="46" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="24" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="18" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="48" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="D23" s="50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="52" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2918,30 +3005,30 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="54" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="56" t="s">
         <v>64</v>
       </c>
     </row>
